--- a/public/inputs/y07-physical-education - input.xlsx
+++ b/public/inputs/y07-physical-education - input.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,22 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001D7A3D"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -55,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,24 +415,19 @@
   </sheetPr>
   <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Section type</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Page</t>
         </is>
@@ -459,9 +444,7 @@
           <t>UNIT 1 · FUTSAL</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>12</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -474,8 +457,10 @@
           <t>1.1 Introduction</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>15</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -489,8 +474,10 @@
           <t>1.2 Warm-ups</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>17</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -504,8 +491,10 @@
           <t>1.3 Ball control</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>19</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -519,8 +508,10 @@
           <t>1.4 Passing</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>21</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -534,8 +525,10 @@
           <t>1.5 Shooting and finishing</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>23</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -549,8 +542,10 @@
           <t>1.6 Goalkeeping</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>25</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -564,8 +559,10 @@
           <t>1.7 Attacking strategies</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>27</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -579,8 +576,10 @@
           <t>1.8 Defensive strategies</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>29</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -594,8 +593,10 @@
           <t>1.9 Game scenarios</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>31</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -609,8 +610,10 @@
           <t>1.10 Cool-down and reflection</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>33</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -624,8 +627,10 @@
           <t>1.11 Collective assessment</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>35</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -639,9 +644,7 @@
           <t>UNIT 2 · CROSS COUNTRY</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>37</v>
-      </c>
+      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -654,8 +657,10 @@
           <t>2.1 Introduction and rules</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>40</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -669,8 +674,10 @@
           <t>2.2 Warm-ups</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>42</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -684,8 +691,10 @@
           <t>2.3 Running techniques</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>44</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -699,8 +708,10 @@
           <t>2.4 Endurance development</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>46</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -714,8 +725,10 @@
           <t>2.5 Race strategies</t>
         </is>
       </c>
-      <c r="C19" t="n">
-        <v>48</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -729,8 +742,10 @@
           <t>2.6 Game scenarios</t>
         </is>
       </c>
-      <c r="C20" t="n">
-        <v>50</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -744,8 +759,10 @@
           <t>2.7 Cool-down and reflection</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>52</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -759,8 +776,10 @@
           <t>2.8 Individual assessment</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>54</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/public/inputs/y07-physical-education - input.xlsx
+++ b/public/inputs/y07-physical-education - input.xlsx
@@ -441,10 +441,9 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UNIT 1 · FUTSAL</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>Unit 1 · Futsal</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -641,10 +640,9 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UNIT 2 · CROSS COUNTRY</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>Unit 2 · Cross Country</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
